--- a/Config/Excel/GameConfig/SkillEffectGroupConfig.xlsx
+++ b/Config/Excel/GameConfig/SkillEffectGroupConfig.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>51001</t>
+          <t>51011</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -511,7 +511,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>玩家普攻效果组</t>
+          <t>玩家普攻效果组（割草增强）</t>
         </is>
       </c>
     </row>
